--- a/equipment-templates/output/download/TEST_Card.xlsx
+++ b/equipment-templates/output/download/TEST_Card.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Card" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Card'!$1:$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,94 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +122,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,892 +547,833 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Поле</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Отметка</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>КАРТОЧКА АППАРАТА №</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Отметка ✓/✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Жёлтые ячейки — ввод вручную  |  Голубые — из базы  |  Колонка «Отметка» — ✓ / ✗ / 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>КАРТОЧКА АППАРАТА № 67+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>22.06.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Инженеры</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Антон / Александр</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>1. ИДЕНТИФИКАЦИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Kyocera ECOSYS M3040dn</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Серийный номер</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>LS67Y43279</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Инвентарный номер</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>67+</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>22.06.2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Инженеры</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Антон / Александр</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1. ИДЕНТИФИКАЦИЯ</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Серийный номер</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Инвентарный номер</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>67+</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Локация (офис/кабинет)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Риелторы (Тюмень)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2. РЕКВИЗИТЫ ДЛЯ АНАЛИЗА</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>IP-адрес</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>MAC-адрес</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Модель картриджа</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Текущий ресурс картриджа (%)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Версия прошивки</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Дата последнего ТО</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Дата последней замены ЗИП</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ответственный у Заказчика</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Контакт (тел/email)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>3. СЧЕТЧИКИ</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Общий пробег (Total)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>272864</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>стр.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ч/Б</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>стр.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Цветной</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>стр.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Сканер</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>стр.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Пробег с последнего ТО</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>стр.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>4. ФИЗИЧЕСКОЕ СОСТОЯНИЕ (отметить ✓ или ✗)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Корпус без трещин, крышки закрываются</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Лоток подачи бумаги: ролики чистые, не лысые, пружины целые</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Лоток выхода: флажки/направляющие целые</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Дуплекс-модуль: нет замятий, засохшего тонера</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Внутренность: нет рассыпанного тонера, бумаги, скрепок</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Кабель питания / USB — целые, с запасом</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr"/>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Шум при работе: нет треска, скрежета, вибрации</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>5. КАЧЕСТВО ПЕЧАТИ (распечатать тестовую страницу из меню)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Равномерная плотность по всей странице</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Нет вертикальных полос / точек / фона</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Нет "волн" и повторяющихся дефектов (шаг дефекта: _____ мм)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr"/>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Регистрация листа ровная (текст не уходит вбок)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr"/>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Тонер закреплен (не смазывается пальцем)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>6. КАЧЕСТВО СКАНИРОВАНИЯ (протестировать на A4 и A3 если есть ADF)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>ADF захватывает лист без перекоса</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>На скане нет полос (проверить стекло и зеркало)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr"/>
+      <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Скан в сетевую папку / на email работает</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Двустороннее сканирование работает (если есть)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr"/>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>7. СУБЪЕКТИВНАЯ ОЦЕНКА СОСТОЯНИЯ (1-5 баллов)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Шкала оценки</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr"/>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>1 — Критическое (не работает / требует срочного ремонта)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>2 — Плохое (работает с перебоями / явные дефекты качества)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>3 — Удовлетворительное (работает, но требует внимания/ТО)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>4 — Хорошее (работает стабильно, мелкие замечания)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>5 — Отличное (идеальное состояние, как новый)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Физическое состояние</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr"/>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
         <is>
           <t>Качество печати</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Качество сканирования</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Общая оценка</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr"/>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Комментарий к оценке</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>8. ЗАМЕЧЕНИЯ И "БОЛЯЧКИ" (свободное описание)</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>9. ПЛАН ДЕЙСТВИЙ (отметить все применимые пункты)</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>[ 1 ] Не требует действий — аппарат в рабочем состоянии</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>[ 2 ] Требуется профилактическая чистка (внутренняя/внешняя)</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>[ 3 ] Требуется плановое ТО (замена роликов, чистка лазера)</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>[ 4 ] Требуется замена ЗИП (указать что</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>[ 5 ] Требуется замена картриджа / тонера</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>[ 6 ] Требуется калибровка цвета (для цветных аппаратов)</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>[ 7 ] Требуется замена термоузла / печки</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>[ 8 ] Требуется перепрошивка / обновление встроенного ПО</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>[ 9 ] Требуется перемещение в другую локацию / кабинет</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>[10 ] Требуется обучение пользователя / инструктаж</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>[11 ] Требуется эскалация в вендора / авторизованный СЦ</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>[12 ] Требуется списание / утилизация (обоснование</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>[13 ] Требуется согласование с Заказчиком (ИТ / АХО)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>[14 ] Требуется срочная закупка расходных материалов</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>[15 ] Аппарат временно выведен из эксплуатации (до</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr"/>
+      <c r="D74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Приоритет выполнения</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>🔴 Критичный  /  🟡 Средний  /  🟢 Плановый</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Срок выполнения</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr"/>
+      <c r="C76" s="6" t="inlineStr"/>
+      <c r="D76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>ПОДПИСИ</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr"/>
+      <c r="C77" s="6" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Антон</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Александр:</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="7" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B48:D48"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D42 D43 D44 D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,✗,—"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D53 D54 D55 D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/equipment-templates/output/download/TEST_Card.xlsx
+++ b/equipment-templates/output/download/TEST_Card.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Card" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Card'!$1:$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,94 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -42,12 +122,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00BF8F00"/>
+      </left>
+      <right style="medium">
+        <color rgb="00BF8F00"/>
+      </right>
+      <top style="medium">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00BF8F00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00C65911"/>
+      </left>
+      <right style="medium">
+        <color rgb="00C65911"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C65911"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00C65911"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -411,892 +575,853 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Поле</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Отметка</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>КАРТОЧКА АППАРАТА №</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Отметка ✓/✗</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Жёлтые ячейки — ввод вручную  |  Голубые — из базы  |  Отметка: ✓ / ✗ / 1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>КАРТОЧКА АППАРАТА № 67+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>23.06.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Инженеры</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Антон / Александр</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>1. ИДЕНТИФИКАЦИЯ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Kyocera ECOSYS M3040dn</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Серийный номер</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>LS67Y43279</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Инвентарный номер</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>67+</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>22.06.2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Инженеры</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Антон / Александр</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1. ИДЕНТИФИКАЦИЯ</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kyocera ECOSYS M3040dn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Серийный номер</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LS67Y43279</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Инвентарный номер</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>67+</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Локация (офис/кабинет)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Риелторы (Тюмень)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2. РЕКВИЗИТЫ ДЛЯ АНАЛИЗА</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>IP-адрес</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>MAC-адрес</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Модель картриджа</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Текущий ресурс картриджа (%)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Версия прошивки</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Дата последнего ТО</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Дата последней замены ЗИП</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="6" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ответственный у Заказчика</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Контакт (тел/email)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>3. СЧЕТЧИКИ</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Общий пробег (Total)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>272864</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>стр.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ч/Б</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>стр.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Цветной</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>стр.</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Сканер</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>стр.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Пробег с последнего ТО</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>стр.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>4. ФИЗИЧЕСКОЕ СОСТОЯНИЕ (отметить ✓ или ✗)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Корпус без трещин, крышки закрываются</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Лоток подачи бумаги: ролики чистые, не лысые, пружины целые</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Лоток выхода: флажки/направляющие целые</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Дуплекс-модуль: нет замятий, засохшего тонера</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Внутренность: нет рассыпанного тонера, бумаги, скрепок</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Кабель питания / USB — целые, с запасом</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr"/>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Шум при работе: нет треска, скрежета, вибрации</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>5. КАЧЕСТВО ПЕЧАТИ (распечатать тестовую страницу из меню)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Равномерная плотность по всей странице</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr"/>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Нет вертикальных полос / точек / фона</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr"/>
+      <c r="C37" s="6" t="inlineStr"/>
+      <c r="D37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Нет "волн" и повторяющихся дефектов (шаг дефекта: _____ мм)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr"/>
+      <c r="C38" s="6" t="inlineStr"/>
+      <c r="D38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Регистрация листа ровная (текст не уходит вбок)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr"/>
+      <c r="C39" s="6" t="inlineStr"/>
+      <c r="D39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Тонер закреплен (не смазывается пальцем)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr"/>
+      <c r="C40" s="6" t="inlineStr"/>
+      <c r="D40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>6. КАЧЕСТВО СКАНИРОВАНИЯ (протестировать на A4 и A3 если есть ADF)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>ADF захватывает лист без перекоса</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr"/>
+      <c r="C42" s="6" t="inlineStr"/>
+      <c r="D42" s="13" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>На скане нет полос (проверить стекло и зеркало)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr"/>
+      <c r="C43" s="6" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Скан в сетевую папку / на email работает</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr"/>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Двустороннее сканирование работает (если есть)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr"/>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>7. СУБЪЕКТИВНАЯ ОЦЕНКА СОСТОЯНИЯ (1-5 баллов)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Шкала оценки</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr"/>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>1 — Критическое (не работает / требует срочного ремонта)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>2 — Плохое (работает с перебоями / явные дефекты качества)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>3 — Удовлетворительное (работает, но требует внимания/ТО)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>4 — Хорошее (работает стабильно, мелкие замечания)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>5 — Отличное (идеальное состояние, как новый)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>Физическое состояние</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr"/>
+      <c r="C53" s="6" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Качество печати</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="13" t="inlineStr"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Качество сканирования</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr"/>
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="13" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Общая оценка</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[ 1 ] [ 2 ] [ 3 ] [ 4 ] [ 5 ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr"/>
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="13" t="inlineStr"/>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Комментарий к оценке</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>8. ЗАМЕЧЕНИЯ И "БОЛЯЧКИ" (свободное описание)</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>9. ПЛАН ДЕЙСТВИЙ (отметить все применимые пункты)</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>[ 1 ] Не требует действий — аппарат в рабочем состоянии</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>[ 2 ] Требуется профилактическая чистка (внутренняя/внешняя)</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>[ 3 ] Требуется плановое ТО (замена роликов, чистка лазера)</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>[ 4 ] Требуется замена ЗИП (указать что</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>[ 5 ] Требуется замена картриджа / тонера</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>[ 6 ] Требуется калибровка цвета (для цветных аппаратов)</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>[ 7 ] Требуется замена термоузла / печки</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>[ 8 ] Требуется перепрошивка / обновление встроенного ПО</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>[ 9 ] Требуется перемещение в другую локацию / кабинет</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>[10 ] Требуется обучение пользователя / инструктаж</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>[11 ] Требуется эскалация в вендора / авторизованный СЦ</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>[12 ] Требуется списание / утилизация (обоснование</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>[13 ] Требуется согласование с Заказчиком (ИТ / АХО)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>[14 ] Требуется срочная закупка расходных материалов</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>[15 ] Аппарат временно выведен из эксплуатации (до</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr"/>
+      <c r="D74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Приоритет выполнения</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>🔴 Критичный  /  🟡 Средний  /  🟢 Плановый</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Срок выполнения</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr"/>
+      <c r="C76" s="6" t="inlineStr"/>
+      <c r="D76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>ПОДПИСИ</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr"/>
+      <c r="C77" s="6" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Антон</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Александр:</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="C78" s="6" t="inlineStr"/>
+      <c r="D78" s="7" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B48:D48"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="D28 D29 D30 D31 D32 D33 D34 D36 D37 D38 D39 D40 D42 D43 D44 D45" showDropDown="1" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,✗,—"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D53 D54 D55 D56" showDropDown="1" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>